--- a/artfynd/A 15047-2024 artfynd.xlsx
+++ b/artfynd/A 15047-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116705135</v>
+        <v>116705113</v>
       </c>
       <c r="B2" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535786</v>
+        <v>535717</v>
       </c>
       <c r="R2" t="n">
-        <v>7193454</v>
+        <v>7193408</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116705131</v>
+        <v>116705165</v>
       </c>
       <c r="B3" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535723</v>
+        <v>535787</v>
       </c>
       <c r="R3" t="n">
-        <v>7193431</v>
+        <v>7193455</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,32 +889,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116705168</v>
+        <v>116705129</v>
       </c>
       <c r="B4" t="n">
-        <v>79556</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535724</v>
+        <v>535684</v>
       </c>
       <c r="R4" t="n">
-        <v>7193431</v>
+        <v>7193397</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,59 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116705099</v>
+        <v>116705130</v>
       </c>
       <c r="B5" t="n">
-        <v>56494</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535776</v>
+        <v>535715</v>
       </c>
       <c r="R5" t="n">
-        <v>7193462</v>
+        <v>7193408</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,59 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116705095</v>
+        <v>116705131</v>
       </c>
       <c r="B6" t="n">
-        <v>57693</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535687</v>
+        <v>535723</v>
       </c>
       <c r="R6" t="n">
-        <v>7193407</v>
+        <v>7193431</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,19 +1210,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116705130</v>
+        <v>116705132</v>
       </c>
       <c r="B7" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1293,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535715</v>
+        <v>535742</v>
       </c>
       <c r="R7" t="n">
-        <v>7193408</v>
+        <v>7193439</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,37 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116705066</v>
+        <v>116705133</v>
       </c>
       <c r="B8" t="n">
-        <v>74553</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535746</v>
+        <v>535741</v>
       </c>
       <c r="R8" t="n">
-        <v>7193446</v>
+        <v>7193472</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1440,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,19 +1424,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116705129</v>
+        <v>116705135</v>
       </c>
       <c r="B9" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1517,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535684</v>
+        <v>535786</v>
       </c>
       <c r="R9" t="n">
-        <v>7193397</v>
+        <v>7193454</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1552,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,59 +1531,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116705098</v>
+        <v>116705136</v>
       </c>
       <c r="B10" t="n">
-        <v>56494</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535683</v>
+        <v>535796</v>
       </c>
       <c r="R10" t="n">
-        <v>7193398</v>
+        <v>7193489</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1673,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,15 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116705113</v>
+        <v>116705066</v>
       </c>
       <c r="B11" t="n">
-        <v>78522</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1726,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1750,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535717</v>
+        <v>535746</v>
       </c>
       <c r="R11" t="n">
-        <v>7193408</v>
+        <v>7193446</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1785,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,32 +1745,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116705132</v>
+        <v>116705168</v>
       </c>
       <c r="B12" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1862,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535742</v>
+        <v>535724</v>
       </c>
       <c r="R12" t="n">
-        <v>7193439</v>
+        <v>7193431</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1897,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,55 +1852,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116705078</v>
+        <v>116705102</v>
       </c>
       <c r="B13" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535724</v>
+        <v>535723</v>
       </c>
       <c r="R13" t="n">
-        <v>7193357</v>
+        <v>7193430</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2014,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,32 +1959,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>116705097</v>
+        <v>116705078</v>
       </c>
       <c r="B14" t="n">
-        <v>56494</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2084,14 +1987,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2100,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535731</v>
+        <v>535724</v>
       </c>
       <c r="R14" t="n">
-        <v>7193365</v>
+        <v>7193357</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2135,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2145,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,50 +2071,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>116705133</v>
+        <v>116705097</v>
       </c>
       <c r="B15" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535741</v>
+        <v>535731</v>
       </c>
       <c r="R15" t="n">
-        <v>7193472</v>
+        <v>7193365</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2247,7 +2150,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2257,7 +2160,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2284,50 +2187,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>116705165</v>
+        <v>116705098</v>
       </c>
       <c r="B16" t="n">
-        <v>82217</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535787</v>
+        <v>535683</v>
       </c>
       <c r="R16" t="n">
-        <v>7193455</v>
+        <v>7193398</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2359,7 +2266,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2276,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,50 +2303,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>116705136</v>
+        <v>116705099</v>
       </c>
       <c r="B17" t="n">
-        <v>78440</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535796</v>
+        <v>535776</v>
       </c>
       <c r="R17" t="n">
-        <v>7193489</v>
+        <v>7193462</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2471,7 +2382,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,7 +2392,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,15 +2419,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>116705106</v>
+        <v>116705095</v>
       </c>
       <c r="B18" t="n">
-        <v>77377</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,34 +2430,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>103001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rödingsjön, Fjällboberg, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535746</v>
+        <v>535687</v>
       </c>
       <c r="R18" t="n">
-        <v>7193447</v>
+        <v>7193407</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2583,7 +2498,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2593,7 +2508,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,37 +2535,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>116705102</v>
+        <v>116705106</v>
       </c>
       <c r="B19" t="n">
-        <v>79557</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2660,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535723</v>
+        <v>535746</v>
       </c>
       <c r="R19" t="n">
-        <v>7193430</v>
+        <v>7193447</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2695,7 +2605,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2705,7 +2615,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
